--- a/data/trans_camb/P16A_n_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-0,96; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-0,79; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,42</t>
+          <t>-0,2; 1,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-1,01; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,1</t>
+          <t>-0,4; 2,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,5</t>
+          <t>-0,37; 0,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,0</t>
+          <t>-0,7; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,98</t>
+          <t>-0,29; 1,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,67</t>
+          <t>-0,12; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,64</t>
+          <t>-0,24; 0,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,78</t>
+          <t>-0,12; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,13</t>
+          <t>-0,31; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,1</t>
+          <t>-0,38; 1,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,95</t>
+          <t>-0,44; 1,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,16</t>
+          <t>-0,08; 1,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,58</t>
+          <t>-0,21; 0,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,97</t>
+          <t>-0,13; 1,06</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,33; —</t>
+          <t>-61,29; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,47</t>
+          <t>-0,43; 1,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; -0,14</t>
+          <t>-1,11; -0,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,25</t>
+          <t>-0,11; 2,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,85</t>
+          <t>-0,52; 1,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,79</t>
+          <t>-0,41; 1,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,22</t>
+          <t>-0,17; 1,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; -0,16</t>
+          <t>-1,11; -0,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,63</t>
+          <t>-0,0; 1,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; inf</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 450,07</t>
+          <t>-44,65; 411,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 101,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 434,69</t>
+          <t>-36,75; 450,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 312,77</t>
+          <t>-22,93; 356,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,23</t>
+          <t>-100,0; 41,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 436,63</t>
+          <t>-9,02; 399,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,37</t>
+          <t>-1,4; 1,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; -0,01</t>
+          <t>-2,24; -0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,22</t>
+          <t>-0,37; 3,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,34</t>
+          <t>-0,98; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,7</t>
+          <t>-1,04; 2,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,53</t>
+          <t>1,99; 6,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,47</t>
+          <t>-0,7; 1,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,06</t>
+          <t>-1,06; 1,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,22</t>
+          <t>0,68; 4,1</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,33; 454,59</t>
+          <t>-84,81; 465,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 843,56</t>
+          <t>-28,76; 860,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 210,21</t>
+          <t>-37,26; 202,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 240,32</t>
+          <t>-38,92; 221,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,06; 556,67</t>
+          <t>53,93; 574,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 167,42</t>
+          <t>-40,01; 151,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 125,75</t>
+          <t>-54,04; 111,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,22; 429,4</t>
+          <t>35,5; 446,82</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,9</t>
+          <t>-2,49; 0,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,87</t>
+          <t>-1,21; 2,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,5</t>
+          <t>1,97; 6,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,05</t>
+          <t>-1,64; 4,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 4,94</t>
+          <t>-1,26; 5,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,22</t>
+          <t>3,05; 8,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,44</t>
+          <t>-1,38; 2,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 3,14</t>
+          <t>-0,77; 3,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,99</t>
+          <t>3,16; 6,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,89; 141,87</t>
+          <t>-89,51; 125,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 363,33</t>
+          <t>-46,79; 383,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44,27; 656,91</t>
+          <t>47,49; 635,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 139,08</t>
+          <t>-24,52; 135,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 140,65</t>
+          <t>-21,87; 155,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,61; 298,23</t>
+          <t>38,74; 279,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 99,13</t>
+          <t>-33,17; 97,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 121,88</t>
+          <t>-19,69; 126,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>67,4; 300,64</t>
+          <t>66,88; 284,01</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,67</t>
+          <t>-2,39; 4,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,71</t>
+          <t>-1,29; 5,79</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,99</t>
+          <t>3,35; 10,1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,99; 10,55</t>
+          <t>1,83; 10,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,45</t>
+          <t>-0,23; 8,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 12,72</t>
+          <t>-3,9; 12,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,57</t>
+          <t>0,51; 6,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,23</t>
+          <t>0,45; 5,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 10,16</t>
+          <t>-0,31; 10,12</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 172,66</t>
+          <t>-45,19; 180,06</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 212,82</t>
+          <t>-27,85; 238,26</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57,76; 406,25</t>
+          <t>55,8; 421,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22,31; 203,07</t>
+          <t>19,39; 218,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 159,4</t>
+          <t>-3,46; 175,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 206,68</t>
+          <t>-35,41; 213,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,85; 147,27</t>
+          <t>6,77; 152,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,36; 145,99</t>
+          <t>4,78; 128,27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,44; 219,17</t>
+          <t>5,54; 210,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 6,91</t>
+          <t>-4,51; 7,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,13</t>
+          <t>-7,09; 3,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,01; 14,0</t>
+          <t>3,13; 13,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,86</t>
+          <t>5,07; 15,43</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,3</t>
+          <t>1,66; 11,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,47; 29,85</t>
+          <t>20,53; 30,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,66</t>
+          <t>3,39; 10,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,37; 7,4</t>
+          <t>-0,11; 7,27</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,4; 22,07</t>
+          <t>15,32; 22,02</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 105,47</t>
+          <t>-37,63; 111,01</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,99; 47,22</t>
+          <t>-53,86; 57,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,34; 199,16</t>
+          <t>18,28; 211,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53,59; 311,23</t>
+          <t>49,04; 288,02</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,83; 218,59</t>
+          <t>13,41; 206,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>200,9; 616,51</t>
+          <t>191,25; 593,36</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,72; 161,8</t>
+          <t>32,41; 176,31</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,0; 121,98</t>
+          <t>-2,58; 108,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>144,83; 346,9</t>
+          <t>142,39; 351,73</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,96</t>
+          <t>-0,36; 0,97</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,77</t>
+          <t>-0,42; 0,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,93</t>
+          <t>1,93; 3,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,36</t>
+          <t>1,43; 3,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,58</t>
+          <t>0,86; 2,67</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,41</t>
+          <t>4,43; 7,4</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,95</t>
+          <t>0,82; 1,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,53</t>
+          <t>0,45; 1,57</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,53</t>
+          <t>3,83; 5,48</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 79,86</t>
+          <t>-22,12; 80,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 64,82</t>
+          <t>-23,26; 67,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>116,41; 317,29</t>
+          <t>114,76; 338,13</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>52,76; 155,56</t>
+          <t>48,5; 153,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,95; 119,1</t>
+          <t>28,45; 119,01</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>166,55; 345,22</t>
+          <t>159,65; 341,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,32; 109,53</t>
+          <t>34,84; 110,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>18,25; 87,22</t>
+          <t>17,68; 88,81</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>170,7; 309,75</t>
+          <t>171,64; 301,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,0</t>
+          <t>-1,06; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,0</t>
+          <t>-0,78; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,44</t>
+          <t>-0,37; 1,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,0</t>
+          <t>-1,09; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,35</t>
+          <t>-0,4; 2,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,48</t>
+          <t>-0,29; 0,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,0</t>
+          <t>-0,69; 0,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,04</t>
+          <t>-0,3; 1,2</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>158,11%</t>
+          <t>179,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,85</t>
+          <t>-0,12; 1,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,65</t>
+          <t>-0,24; 0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,74</t>
+          <t>-0,12; 1,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,22</t>
+          <t>-0,3; 1,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,05</t>
+          <t>-0,36; 1,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,08</t>
+          <t>-0,49; 0,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,11</t>
+          <t>-0,06; 1,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,58</t>
+          <t>-0,19; 0,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,06</t>
+          <t>-0,17; 0,95</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>387,43%</t>
+          <t>344,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>147,88%</t>
+          <t>134,83%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,29; —</t>
+          <t>-63,83; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,35</t>
+          <t>-0,41; 1,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; -0,13</t>
+          <t>-1,25; -0,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,36</t>
+          <t>-0,23; 1,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,79</t>
+          <t>-0,49; 1,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,13</t>
+          <t>-1,53; 0,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,81</t>
+          <t>-0,19; 2,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,25</t>
+          <t>-0,19; 1,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; -0,1</t>
+          <t>-1,05; -0,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 1,56</t>
+          <t>-0,01; 1,55</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180,39%</t>
+          <t>148,88%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>110,59%</t>
+          <t>111,71%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-87,59; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,18; 1387,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 411,64</t>
+          <t>-39,28; 383,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,9</t>
+          <t>-100,0; 103,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,75; 450,56</t>
+          <t>-29,15; 517,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 356,95</t>
+          <t>-29,0; 304,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,07</t>
+          <t>-100,0; 1,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 399,62</t>
+          <t>-10,04; 385,32</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,41</t>
+          <t>-1,37; 1,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,03</t>
+          <t>-2,13; -0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,36</t>
+          <t>0,82; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,39</t>
+          <t>-1,07; 2,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,49</t>
+          <t>-0,94; 2,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,67</t>
+          <t>1,66; 5,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,44</t>
+          <t>-0,77; 1,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,02</t>
+          <t>-1,14; 0,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,1</t>
+          <t>1,73; 4,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167,32%</t>
+          <t>258,85%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>200,27%</t>
+          <t>178,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>177,09%</t>
+          <t>206,34%</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,81; 465,43</t>
+          <t>-82,27; 483,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 860,03</t>
+          <t>12,38; 1454,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 202,43</t>
+          <t>-41,65; 197,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 221,65</t>
+          <t>-34,54; 238,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,93; 574,04</t>
+          <t>43,02; 444,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 151,39</t>
+          <t>-39,79; 144,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,04; 111,07</t>
+          <t>-55,68; 106,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,5; 446,82</t>
+          <t>70,44; 490,46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>5,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,94</t>
+          <t>-2,66; 0,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,96</t>
+          <t>-1,34; 2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,26</t>
+          <t>1,72; 6,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,77</t>
+          <t>-1,24; 4,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 5,03</t>
+          <t>-1,28; 5,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,99</t>
+          <t>3,23; 8,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,4</t>
+          <t>-1,35; 2,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,09</t>
+          <t>-0,82; 2,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,95</t>
+          <t>3,34; 7,09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>234,83%</t>
+          <t>226,02%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>123,78%</t>
+          <t>126,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>150,39%</t>
+          <t>151,05%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-89,51; 125,81</t>
+          <t>-89,22; 150,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,79; 383,64</t>
+          <t>-51,83; 311,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47,49; 635,94</t>
+          <t>40,81; 656,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 135,95</t>
+          <t>-22,05; 151,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,87; 155,11</t>
+          <t>-20,63; 157,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,74; 279,21</t>
+          <t>45,27; 273,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 97,83</t>
+          <t>-31,83; 89,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 126,91</t>
+          <t>-18,78; 109,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>66,88; 284,01</t>
+          <t>71,56; 291,44</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>11,74</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>8,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 4,52</t>
+          <t>-2,39; 4,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,79</t>
+          <t>-1,19; 5,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,1</t>
+          <t>2,72; 8,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,9</t>
+          <t>1,72; 10,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 8,62</t>
+          <t>-0,07; 8,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 12,85</t>
+          <t>8,11; 15,67</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,36</t>
+          <t>0,69; 6,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,77</t>
+          <t>0,36; 5,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 10,12</t>
+          <t>6,49; 11,39</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>170,1%</t>
+          <t>152,98%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>169,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>109,3%</t>
+          <t>160,86%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 180,06</t>
+          <t>-48,27; 171,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 238,26</t>
+          <t>-23,24; 212,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55,8; 421,19</t>
+          <t>43,12; 379,76</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19,39; 218,5</t>
+          <t>19,08; 213,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 175,19</t>
+          <t>-5,53; 159,46</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 213,89</t>
+          <t>82,22; 302,75</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,77; 152,97</t>
+          <t>8,8; 147,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4,78; 128,27</t>
+          <t>5,21; 134,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5,54; 210,45</t>
+          <t>85,62; 264,85</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,67</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,57</t>
+          <t>25,29</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,86</t>
+          <t>18,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 7,64</t>
+          <t>-4,15; 7,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 3,69</t>
+          <t>-6,31; 3,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,82</t>
+          <t>3,54; 14,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,07; 15,43</t>
+          <t>5,15; 15,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,05</t>
+          <t>2,43; 11,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,53; 30,02</t>
+          <t>20,83; 29,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,98</t>
+          <t>2,87; 10,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,27</t>
+          <t>-0,24; 7,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,32; 22,02</t>
+          <t>15,36; 22,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>350,81%</t>
+          <t>346,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>229,02%</t>
+          <t>228,19%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-37,63; 111,01</t>
+          <t>-34,65; 118,53</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,86; 57,24</t>
+          <t>-48,68; 60,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18,28; 211,57</t>
+          <t>23,74; 205,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49,04; 288,02</t>
+          <t>45,42; 283,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>13,41; 206,72</t>
+          <t>18,75; 209,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>191,25; 593,36</t>
+          <t>203,06; 608,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,41; 176,31</t>
+          <t>28,17; 167,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 108,9</t>
+          <t>-2,73; 109,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>142,39; 351,73</t>
+          <t>141,23; 365,63</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,05</t>
+          <t>3,26</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>5,17</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,97</t>
+          <t>-0,3; 1,03</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,8</t>
+          <t>-0,46; 0,74</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,93; 3,81</t>
+          <t>2,53; 4,03</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,33</t>
+          <t>1,42; 3,36</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,67</t>
+          <t>0,85; 2,63</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,4</t>
+          <t>6,14; 7,96</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,98</t>
+          <t>0,81; 1,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,57</t>
+          <t>0,48; 1,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,48</t>
+          <t>4,58; 5,79</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>206,2%</t>
+          <t>220,72%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>245,29%</t>
+          <t>270,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>233,43%</t>
+          <t>254,44%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 80,19</t>
+          <t>-18,88; 83,42</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 67,84</t>
+          <t>-25,56; 61,66</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>114,76; 338,13</t>
+          <t>132,18; 336,07</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>48,5; 153,73</t>
+          <t>47,55; 151,93</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28,45; 119,01</t>
+          <t>27,81; 120,08</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>159,65; 341,34</t>
+          <t>196,02; 362,5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,84; 110,5</t>
+          <t>35,65; 110,03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,68; 88,81</t>
+          <t>20,41; 83,26</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>171,64; 301,54</t>
+          <t>197,55; 333,65</t>
         </is>
       </c>
     </row>
